--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74553567</v>
       </c>
       <c r="B2" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106991</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582761.9249892279</v>
+        <v>582762</v>
       </c>
       <c r="R2" t="n">
-        <v>6317142.433282511</v>
+        <v>6317142</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1992-07-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1992-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74948082</v>
       </c>
       <c r="B3" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582861.8254387751</v>
+        <v>582862</v>
       </c>
       <c r="R3" t="n">
-        <v>6317143.336594853</v>
+        <v>6317143</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1992-07-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1992-07-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553567</v>
       </c>
       <c r="B2" t="n">
-        <v>106991</v>
+        <v>107000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74948082</v>
       </c>
       <c r="B3" t="n">
-        <v>110704</v>
+        <v>110713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553567</v>
       </c>
       <c r="B2" t="n">
-        <v>107000</v>
+        <v>107005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74948082</v>
       </c>
       <c r="B3" t="n">
-        <v>110713</v>
+        <v>110718</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553567</v>
       </c>
       <c r="B2" t="n">
-        <v>107005</v>
+        <v>107033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74948082</v>
       </c>
       <c r="B3" t="n">
-        <v>110718</v>
+        <v>110746</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553567</v>
       </c>
       <c r="B2" t="n">
-        <v>107033</v>
+        <v>107039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74948082</v>
       </c>
       <c r="B3" t="n">
-        <v>110746</v>
+        <v>110752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553567</v>
       </c>
       <c r="B2" t="n">
-        <v>107039</v>
+        <v>107046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74948082</v>
       </c>
       <c r="B3" t="n">
-        <v>110752</v>
+        <v>110759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553567</v>
       </c>
       <c r="B2" t="n">
-        <v>107046</v>
+        <v>107050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74948082</v>
       </c>
       <c r="B3" t="n">
-        <v>110759</v>
+        <v>110763</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553567</v>
       </c>
       <c r="B2" t="n">
-        <v>107050</v>
+        <v>107058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74948082</v>
       </c>
       <c r="B3" t="n">
-        <v>110763</v>
+        <v>110771</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553567</v>
       </c>
       <c r="B2" t="n">
-        <v>107061</v>
+        <v>107066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74948082</v>
       </c>
       <c r="B3" t="n">
-        <v>110774</v>
+        <v>110779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553567</v>
       </c>
       <c r="B2" t="n">
-        <v>107066</v>
+        <v>107074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74948082</v>
       </c>
       <c r="B3" t="n">
-        <v>110779</v>
+        <v>110787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74553567</v>
       </c>
       <c r="B2" t="n">
-        <v>107074</v>
+        <v>107084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74948082</v>
       </c>
       <c r="B3" t="n">
-        <v>110787</v>
+        <v>110797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>74553567</v>
       </c>
       <c r="B2" t="n">
-        <v>107084</v>
+        <v>107608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,11 +789,11 @@
         <v>74948082</v>
       </c>
       <c r="B3" t="n">
-        <v>110797</v>
+        <v>111389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -890,6 +890,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>74119478</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101896</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nyebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>582862</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6317143</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1992-07-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1992-07-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 5G3g 3339. SOM: Chrysosplenium alternifolium. LEG: Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bäck</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 16431-2023 artfynd.xlsx
+++ b/artfynd/A 16431-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74553567</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74948082</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74119478</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>